--- a/output/laminas_provinciales/prov_i_ingr_median_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2022_magallanes.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -408,7 +408,7 @@
         <v>712500</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -426,7 +426,7 @@
         <v>853542</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -444,13 +444,13 @@
         <v>784320</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -459,25 +459,16 @@
         </is>
       </c>
       <c r="C5">
-        <v>751280</v>
-      </c>
-      <c r="D5">
-        <v>685620</v>
-      </c>
-      <c r="E5">
-        <v>65660</v>
-      </c>
-      <c r="F5">
-        <v>9.576733467518462</v>
+        <v>751950.5</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -486,25 +477,16 @@
         </is>
       </c>
       <c r="C6">
-        <v>936021</v>
-      </c>
-      <c r="D6">
-        <v>824910</v>
-      </c>
-      <c r="E6">
-        <v>111111</v>
-      </c>
-      <c r="F6">
-        <v>13.46946939666145</v>
+        <v>952186.5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -513,25 +495,16 @@
         </is>
       </c>
       <c r="C7">
-        <v>855529</v>
-      </c>
-      <c r="D7">
-        <v>761867.5</v>
-      </c>
-      <c r="E7">
-        <v>93661.5</v>
-      </c>
-      <c r="F7">
-        <v>12.29367311245067</v>
+        <v>864624</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Tierra del Fuego</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -540,16 +513,16 @@
         </is>
       </c>
       <c r="C8">
-        <v>751950.5</v>
+        <v>831087</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Tierra del Fuego</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -558,16 +531,16 @@
         </is>
       </c>
       <c r="C9">
-        <v>952186.5</v>
+        <v>932360</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Tierra del Fuego</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -576,16 +549,16 @@
         </is>
       </c>
       <c r="C10">
-        <v>864624</v>
+        <v>883969</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -594,16 +567,16 @@
         </is>
       </c>
       <c r="C11">
-        <v>831087</v>
+        <v>893340</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -612,16 +585,16 @@
         </is>
       </c>
       <c r="C12">
-        <v>932360</v>
+        <v>1018189</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -630,63 +603,9 @@
         </is>
       </c>
       <c r="C13">
-        <v>883969</v>
+        <v>958111</v>
       </c>
       <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Antártica Chilena</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>893340</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Antártica Chilena</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>1018189</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Antártica Chilena</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>958111</v>
-      </c>
-      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -759,7 +678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1000,60 +919,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>855529</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>958425</v>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>1017970</v>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2022_magallanes.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">prov_rank</t>
   </si>
   <si>
-    <t xml:space="preserve">Ultima Esperanza</t>
+    <t xml:space="preserve">Última Esperanza</t>
   </si>
   <si>
     <t xml:space="preserve">Femenino</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:11</t>
+    <t xml:space="preserve">2026-08-19 13:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -83,13 +83,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_median_a_2022_magallanes.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Mediana ingreso de asalariados dependientes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Magallanes</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -761,23 +767,23 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -857,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -868,7 +874,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>958111</v>
@@ -879,7 +885,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1056040</v>
@@ -890,7 +896,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1170860</v>
@@ -901,7 +907,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>864624</v>
@@ -912,7 +918,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>968400</v>
@@ -923,7 +929,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>1026198</v>
@@ -934,7 +940,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>883969</v>
@@ -945,7 +951,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>997088</v>
@@ -956,7 +962,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1033228</v>
@@ -967,7 +973,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>784320</v>
@@ -978,7 +984,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>894500</v>
@@ -989,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>971418</v>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2022_magallanes.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:48</t>
+    <t xml:space="preserve">2026-09-07 11:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
